--- a/currentbuild/StructureDefinition-no-basis-auditevent.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-auditevent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.2</t>
+    <t>0.8.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T06:42:57+00:00</t>
+    <t>2024-03-15T09:00:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This is the main profile that describes the mapping [Norwegian Common Trust Framework attributes ("NHN felles tillitsrammeverk")](https://github.com/NorskHelsenett/Tillitsrammeverk/blob/main/specs/informasjons_og_datamodell.md#424-oppsummering-av-informasjonselementer) to AuditEvent Resource.</t>
+    <t>This is the main profile that describes the mapping [Norwegian Trust Framework attributes ("Tillitsrammeverk")](https://github.com/NorskHelsenett/Tillitsrammeverk/blob/main/specs/informasjons_og_datamodell.md#424-oppsummering-av-informasjonselementer) to AuditEvent Resource.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/currentbuild/StructureDefinition-no-basis-auditevent.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-auditevent.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$101</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3870" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.3</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T09:00:42+00:00</t>
+    <t>2024-03-17T09:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -501,7 +501,10 @@
 </t>
   </si>
   <si>
-    <t>care-relationship:decision-ref:id, :description, :user-selected</t>
+    <t>toa, care-relationship:decision-ref:id, :description, :user-selected</t>
+  </si>
+  <si>
+    <t>This extension is used to carry attributes from Norwegian Trust Framework (Nasjonalt tillitsrammeverk) which there exists no natural element for.</t>
   </si>
   <si>
     <t>AuditEvent.extension:_careRelationMetaData.id</t>
@@ -532,34 +535,34 @@
     <t>AuditEvent.extension.extension</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Element.extension</t>
   </si>
   <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:id</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:id.id</t>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-id</t>
+  </si>
+  <si>
+    <t>decision-ref-id</t>
+  </si>
+  <si>
+    <t>care-relationship:decision-ref:id</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-id.id</t>
   </si>
   <si>
     <t>AuditEvent.extension.extension.id</t>
   </si>
   <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:id.extension</t>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-id.extension</t>
   </si>
   <si>
     <t>AuditEvent.extension.extension.extension</t>
   </si>
   <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:id.url</t>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-id.url</t>
   </si>
   <si>
     <t>AuditEvent.extension.extension.url</t>
@@ -577,65 +580,84 @@
     <t>Extension.url</t>
   </si>
   <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:id.value[x]</t>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-id.value[x]</t>
   </si>
   <si>
     <t>AuditEvent.extension.extension.value[x]</t>
   </si>
   <si>
-    <t>care-relationship:decision-ref:id</t>
-  </si>
-  <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:description</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:description.id</t>
-  </si>
-  <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:description.extension</t>
-  </si>
-  <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:description.url</t>
-  </si>
-  <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:description.value[x]</t>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-description</t>
+  </si>
+  <si>
+    <t>decision-ref-description</t>
   </si>
   <si>
     <t>care-relationship:decision-ref:description</t>
   </si>
   <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:user-selected</t>
-  </si>
-  <si>
-    <t>user-selected</t>
-  </si>
-  <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:user-selected.id</t>
-  </si>
-  <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:user-selected.extension</t>
-  </si>
-  <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:user-selected.url</t>
-  </si>
-  <si>
-    <t>AuditEvent.extension:_careRelationMetaData.extension:user-selected.value[x]</t>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-description.id</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-description.extension</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-description.url</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-description.value[x]</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-user-selected</t>
+  </si>
+  <si>
+    <t>decision-ref-user-selected</t>
+  </si>
+  <si>
+    <t>care-relationship:decision-ref:user-selected</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-user-selected.id</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-user-selected.extension</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-user-selected.url</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:decision-ref-user-selected.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>care-relationship:decision-ref:user-selected</t>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:toa</t>
+  </si>
+  <si>
+    <t>toa</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:toa.id</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:toa.extension</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:toa.url</t>
+  </si>
+  <si>
+    <t>AuditEvent.extension:_careRelationMetaData.extension:toa.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
   </si>
   <si>
     <t>AuditEvent.extension:_careRelationMetaData.url</t>
@@ -885,10 +907,7 @@
     <t>Use AuditEvent.agent.purposeOfUse when you know that it is specific to the agent, otherwise use AuditEvent.purposeOfEvent. For example, during a machine-to-machine transfer it might not be obvious to the audit system who caused the event, but it does know why.</t>
   </si>
   <si>
-    <t>The reason the activity took place.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
+    <t>urn:no-basis-auditevent/ValueSet/no-basis-auditevent-purpose-of-event</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1441,6 +1460,12 @@
   </si>
   <si>
     <t>Use AuditEvent.agent.purposeOfUse when you know that is specific to the agent, otherwise use AuditEvent.purposeOfEvent. For example, during a machine-to-machine transfer it might not be obvious to the audit system who caused the event, but it does know why.</t>
+  </si>
+  <si>
+    <t>The reason the activity took place.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
   </si>
   <si>
     <t>*.reasonCode [ActHealthInformationPurposeOfUseReason codes/v:PurposeOfUse
@@ -2167,12 +2192,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP96"/>
+  <dimension ref="A1:AP101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="74.80078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="86.2109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.71484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.44921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="24.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2195,7 +2220,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="75.9609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.78125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.0078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3571,7 +3596,7 @@
         <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3657,10 +3682,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3683,13 +3708,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3740,7 +3765,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3758,7 +3783,7 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3775,10 +3800,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3786,7 +3811,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>79</v>
@@ -3896,7 +3921,7 @@
         <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>169</v>
@@ -3906,7 +3931,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>89</v>
@@ -3924,7 +3949,7 @@
         <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
         <v>136</v>
@@ -4013,10 +4038,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4039,13 +4064,13 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4096,7 +4121,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4114,7 +4139,7 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -4131,10 +4156,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4249,10 +4274,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4278,13 +4303,13 @@
         <v>103</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4334,7 +4359,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -4369,10 +4394,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4395,10 +4420,10 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="M19" t="s" s="2">
         <v>183</v>
@@ -4490,7 +4515,7 @@
         <v>185</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>186</v>
@@ -4500,7 +4525,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -4518,7 +4543,7 @@
         <v>134</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>135</v>
+        <v>187</v>
       </c>
       <c r="M20" t="s" s="2">
         <v>136</v>
@@ -4607,10 +4632,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4633,13 +4658,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4690,7 +4715,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4708,7 +4733,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4725,10 +4750,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4843,10 +4868,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4872,13 +4897,13 @@
         <v>103</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4928,7 +4953,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>89</v>
@@ -4963,10 +4988,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4989,10 +5014,10 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>183</v>
@@ -5084,7 +5109,7 @@
         <v>192</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>193</v>
@@ -5094,7 +5119,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>89</v>
@@ -5112,7 +5137,7 @@
         <v>134</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>135</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
         <v>136</v>
@@ -5201,10 +5226,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5227,13 +5252,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5284,7 +5309,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5302,7 +5327,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -5319,10 +5344,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5437,10 +5462,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5466,13 +5491,13 @@
         <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5522,7 +5547,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>89</v>
@@ -5557,10 +5582,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5583,10 +5608,10 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M29" t="s" s="2">
         <v>183</v>
@@ -5678,9 +5703,11 @@
         <v>200</v>
       </c>
       <c r="B30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C30" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5701,24 +5728,22 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>77</v>
@@ -5760,25 +5785,25 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5795,10 +5820,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5809,7 +5834,7 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5821,13 +5846,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5878,7 +5903,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5890,13 +5915,13 @@
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5913,27 +5938,27 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
         <v>77</v>
@@ -5942,17 +5967,13 @@
         <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5988,19 +6009,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6018,7 +6039,7 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -6035,10 +6056,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6058,27 +6079,27 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>215</v>
+        <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>77</v>
@@ -6096,13 +6117,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>220</v>
+        <v>77</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>221</v>
+        <v>77</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -6120,7 +6141,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>89</v>
@@ -6132,22 +6153,22 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>77</v>
@@ -6155,10 +6176,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6169,7 +6190,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -6178,21 +6199,19 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>229</v>
+        <v>183</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -6216,13 +6235,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>231</v>
+        <v>77</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -6240,13 +6259,13 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
@@ -6258,13 +6277,13 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>77</v>
@@ -6275,10 +6294,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6286,7 +6305,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -6298,27 +6317,27 @@
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>77</v>
@@ -6336,13 +6355,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>240</v>
+        <v>77</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -6360,10 +6379,10 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>89</v>
@@ -6372,19 +6391,19 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>223</v>
+        <v>132</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>241</v>
+        <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>77</v>
@@ -6395,10 +6414,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6409,7 +6428,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -6421,17 +6440,15 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>246</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6480,7 +6497,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>242</v>
+        <v>184</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6495,65 +6512,65 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>248</v>
+        <v>132</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>249</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>250</v>
+        <v>77</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>253</v>
+        <v>214</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>253</v>
+        <v>214</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>254</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>256</v>
+        <v>217</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>257</v>
+        <v>218</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6602,45 +6619,45 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>259</v>
+        <v>132</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>260</v>
+        <v>77</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>262</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6648,7 +6665,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>89</v>
@@ -6663,18 +6680,18 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6698,13 +6715,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6722,10 +6739,10 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>89</v>
@@ -6737,19 +6754,19 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>77</v>
+        <v>229</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>268</v>
+        <v>230</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>77</v>
@@ -6757,10 +6774,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6771,7 +6788,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -6783,16 +6800,18 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6816,13 +6835,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6840,13 +6859,13 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
@@ -6858,13 +6877,13 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>274</v>
+        <v>240</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>77</v>
@@ -6875,10 +6894,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6889,7 +6908,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -6901,18 +6920,18 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>276</v>
+        <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>277</v>
+        <v>242</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6936,13 +6955,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6960,13 +6979,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>275</v>
+        <v>241</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
@@ -6975,30 +6994,30 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>283</v>
+        <v>230</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>285</v>
+        <v>232</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>286</v>
+        <v>77</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7021,15 +7040,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>158</v>
+        <v>250</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -7078,7 +7099,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>161</v>
+        <v>249</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7090,44 +7111,44 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -7136,21 +7157,23 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>134</v>
+        <v>261</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -7186,57 +7209,57 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>167</v>
+        <v>260</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>162</v>
+        <v>266</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7247,7 +7270,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -7259,20 +7282,18 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>215</v>
+        <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
       </c>
@@ -7296,13 +7317,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>77</v>
+        <v>272</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7320,13 +7341,13 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -7338,13 +7359,13 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>77</v>
@@ -7355,10 +7376,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7378,16 +7399,16 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>159</v>
+        <v>278</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>160</v>
+        <v>279</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7438,7 +7459,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>161</v>
+        <v>277</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7450,19 +7471,19 @@
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>162</v>
+        <v>280</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>77</v>
@@ -7473,14 +7494,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7496,19 +7517,19 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>134</v>
+        <v>283</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>211</v>
+        <v>286</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7534,31 +7555,29 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>167</v>
+        <v>282</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7570,33 +7589,33 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>77</v>
+        <v>288</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>162</v>
+        <v>289</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7616,23 +7635,19 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>302</v>
+        <v>160</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -7680,7 +7695,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>306</v>
+        <v>162</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7692,13 +7707,13 @@
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>307</v>
+        <v>163</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7715,21 +7730,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -7738,19 +7753,19 @@
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>311</v>
+        <v>218</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7788,37 +7803,37 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>312</v>
+        <v>167</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>313</v>
+        <v>163</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -7835,10 +7850,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7849,7 +7864,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -7861,17 +7876,19 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7920,13 +7937,13 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
@@ -7938,7 +7955,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7955,10 +7972,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7978,21 +7995,19 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>321</v>
+        <v>160</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>322</v>
+        <v>161</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>323</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -8040,7 +8055,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>162</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8052,13 +8067,13 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -8075,21 +8090,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -8098,23 +8113,21 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>327</v>
+        <v>296</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -8150,37 +8163,37 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>331</v>
+        <v>167</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>332</v>
+        <v>163</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -8197,10 +8210,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8223,19 +8236,19 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -8284,7 +8297,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8302,7 +8315,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8319,21 +8332,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>341</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -8342,23 +8355,21 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>342</v>
+        <v>159</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -8406,13 +8417,13 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
@@ -8421,30 +8432,30 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>349</v>
+        <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>352</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8464,19 +8475,21 @@
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>159</v>
+        <v>321</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>160</v>
+        <v>322</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -8524,7 +8537,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>161</v>
+        <v>324</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8536,13 +8549,13 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>162</v>
+        <v>325</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -8559,21 +8572,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -8582,21 +8595,21 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>290</v>
+        <v>327</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -8644,25 +8657,25 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>167</v>
+        <v>330</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>162</v>
+        <v>331</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8679,45 +8692,45 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>211</v>
+        <v>335</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>212</v>
+        <v>336</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8766,25 +8779,25 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>132</v>
+        <v>338</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8801,10 +8814,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8824,19 +8837,23 @@
         <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>276</v>
+        <v>159</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8860,13 +8877,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>363</v>
+        <v>77</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8884,7 +8901,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8899,38 +8916,38 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>367</v>
+        <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>368</v>
+        <v>77</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>369</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>77</v>
+        <v>347</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>79</v>
@@ -8945,19 +8962,19 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>276</v>
+        <v>348</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>372</v>
+        <v>350</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8982,13 +8999,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>375</v>
+        <v>77</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>376</v>
+        <v>77</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>377</v>
+        <v>77</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -9006,10 +9023,10 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>79</v>
@@ -9021,34 +9038,34 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>77</v>
+        <v>353</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>379</v>
+        <v>358</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>381</v>
+        <v>77</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9064,23 +9081,19 @@
         <v>77</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>382</v>
+        <v>159</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>383</v>
+        <v>160</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -9128,7 +9141,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>162</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9140,44 +9153,44 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>387</v>
+        <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>388</v>
+        <v>163</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>390</v>
+        <v>77</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>391</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>392</v>
+        <v>360</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>392</v>
+        <v>360</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
@@ -9189,18 +9202,18 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>393</v>
+        <v>296</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -9248,34 +9261,34 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>392</v>
+        <v>167</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>396</v>
+        <v>163</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>397</v>
+        <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>390</v>
+        <v>77</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>77</v>
@@ -9283,43 +9296,45 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>361</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>398</v>
+        <v>361</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>399</v>
+        <v>363</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>401</v>
+        <v>219</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9368,34 +9383,34 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>398</v>
+        <v>365</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>402</v>
+        <v>132</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>403</v>
+        <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>390</v>
+        <v>77</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>77</v>
@@ -9403,10 +9418,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9414,7 +9429,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>89</v>
@@ -9426,23 +9441,19 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>198</v>
+        <v>283</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>405</v>
+        <v>367</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
       </c>
@@ -9466,13 +9477,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -9490,10 +9501,10 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>89</v>
@@ -9505,30 +9516,30 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>409</v>
+        <v>372</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>410</v>
+        <v>373</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9539,7 +9550,7 @@
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -9551,16 +9562,20 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>412</v>
+        <v>283</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>413</v>
+        <v>377</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -9584,13 +9599,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>77</v>
+        <v>382</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>77</v>
+        <v>383</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -9608,13 +9623,13 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>77</v>
@@ -9623,41 +9638,41 @@
         <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>416</v>
+        <v>384</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>417</v>
+        <v>356</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>418</v>
+        <v>374</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>419</v>
+        <v>385</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>77</v>
+        <v>387</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
@@ -9666,22 +9681,22 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>103</v>
+        <v>388</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>422</v>
+        <v>390</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>423</v>
+        <v>391</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>424</v>
+        <v>392</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9730,13 +9745,13 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
@@ -9745,30 +9760,30 @@
         <v>101</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>77</v>
+        <v>393</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>285</v>
+        <v>356</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>77</v>
+        <v>396</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>427</v>
+        <v>397</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9791,17 +9806,17 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9826,13 +9841,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>432</v>
+        <v>77</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>433</v>
+        <v>77</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9850,7 +9865,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9868,16 +9883,16 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>435</v>
+        <v>403</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>417</v>
+        <v>356</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>77</v>
+        <v>396</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>77</v>
@@ -9885,10 +9900,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9911,16 +9926,18 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>342</v>
+        <v>159</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>438</v>
+        <v>406</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9968,7 +9985,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>436</v>
+        <v>404</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9986,16 +10003,16 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>417</v>
+        <v>356</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>77</v>
+        <v>396</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>77</v>
@@ -10003,10 +10020,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10014,7 +10031,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
@@ -10026,19 +10043,23 @@
         <v>77</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>159</v>
+        <v>411</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -10086,10 +10107,10 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>161</v>
+        <v>410</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>89</v>
@@ -10098,19 +10119,19 @@
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>162</v>
+        <v>415</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>77</v>
+        <v>416</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>77</v>
+        <v>356</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>77</v>
@@ -10121,21 +10142,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -10147,17 +10168,15 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>134</v>
+        <v>418</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>290</v>
+        <v>419</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10206,49 +10225,49 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>167</v>
+        <v>417</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>77</v>
+        <v>421</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>162</v>
+        <v>422</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>77</v>
+        <v>423</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>77</v>
+        <v>424</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>77</v>
+        <v>425</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10261,25 +10280,25 @@
         <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>357</v>
+        <v>427</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>358</v>
+        <v>428</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>211</v>
+        <v>429</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>212</v>
+        <v>430</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10328,7 +10347,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>359</v>
+        <v>426</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10340,33 +10359,33 @@
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>132</v>
+        <v>431</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>77</v>
+        <v>291</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>77</v>
+        <v>433</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10389,19 +10408,17 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -10426,13 +10443,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>77</v>
+        <v>438</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>77</v>
+        <v>439</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10450,7 +10467,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10468,16 +10485,16 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>450</v>
+        <v>77</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>77</v>
@@ -10485,10 +10502,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10511,18 +10528,16 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>109</v>
+        <v>348</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>454</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
@@ -10546,13 +10561,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>238</v>
+        <v>77</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>455</v>
+        <v>77</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>456</v>
+        <v>77</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -10570,7 +10585,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10588,13 +10603,13 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>457</v>
+        <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>77</v>
@@ -10605,10 +10620,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10619,7 +10634,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -10631,17 +10646,15 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>276</v>
+        <v>159</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>459</v>
+        <v>160</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10666,13 +10679,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>280</v>
+        <v>77</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10690,34 +10703,34 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>458</v>
+        <v>162</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>462</v>
+        <v>163</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>463</v>
+        <v>77</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>77</v>
@@ -10725,21 +10738,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -10751,20 +10764,18 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>465</v>
+        <v>296</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>466</v>
+        <v>297</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>468</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -10812,31 +10823,31 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>464</v>
+        <v>167</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>469</v>
+        <v>163</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>470</v>
+        <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>471</v>
+        <v>77</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>77</v>
@@ -10847,42 +10858,46 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>159</v>
+        <v>363</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10930,25 +10945,25 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>161</v>
+        <v>365</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10965,21 +10980,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -10991,18 +11006,20 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>290</v>
+        <v>450</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>291</v>
+        <v>451</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -11050,34 +11067,34 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>167</v>
+        <v>449</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>162</v>
+        <v>454</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>77</v>
+        <v>455</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>77</v>
+        <v>423</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>77</v>
+        <v>456</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>77</v>
@@ -11085,45 +11102,43 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>357</v>
+        <v>458</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>212</v>
+        <v>460</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11148,13 +11163,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>77</v>
+        <v>461</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -11172,31 +11187,31 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>359</v>
+        <v>457</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>132</v>
+        <v>454</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>77</v>
+        <v>463</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>77</v>
+        <v>423</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>77</v>
@@ -11207,10 +11222,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11221,7 +11236,7 @@
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
@@ -11233,18 +11248,18 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>158</v>
+        <v>283</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>478</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -11268,13 +11283,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>77</v>
+        <v>468</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>77</v>
+        <v>469</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -11292,13 +11307,13 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>77</v>
@@ -11310,16 +11325,16 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>480</v>
+        <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AO76" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>77</v>
@@ -11327,14 +11342,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>482</v>
+        <v>77</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11350,20 +11365,22 @@
         <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>483</v>
+        <v>348</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="O77" t="s" s="2">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -11412,7 +11429,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>89</v>
@@ -11430,13 +11447,13 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>388</v>
+        <v>477</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>77</v>
@@ -11447,10 +11464,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11461,7 +11478,7 @@
         <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -11473,18 +11490,16 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>489</v>
+        <v>160</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>490</v>
+        <v>161</v>
       </c>
       <c r="N78" s="2"/>
-      <c r="O78" t="s" s="2">
-        <v>491</v>
-      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
       </c>
@@ -11508,13 +11523,13 @@
         <v>77</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>492</v>
+        <v>77</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>493</v>
+        <v>77</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -11532,31 +11547,31 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>488</v>
+        <v>162</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>494</v>
+        <v>163</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>495</v>
+        <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>471</v>
+        <v>77</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11567,14 +11582,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>497</v>
+        <v>215</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11593,20 +11608,18 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>342</v>
+        <v>134</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>498</v>
+        <v>296</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>499</v>
+        <v>297</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11654,7 +11667,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>496</v>
+        <v>167</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11666,65 +11679,69 @@
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>502</v>
+        <v>140</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>503</v>
+        <v>163</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>504</v>
+        <v>77</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>225</v>
+        <v>77</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>505</v>
+        <v>77</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>506</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>159</v>
+        <v>363</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -11772,25 +11789,25 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>161</v>
+        <v>365</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11807,21 +11824,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>508</v>
+        <v>483</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>508</v>
+        <v>483</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -11833,18 +11850,18 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>290</v>
+        <v>484</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>485</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>486</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
       </c>
@@ -11892,31 +11909,31 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>167</v>
+        <v>483</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>162</v>
+        <v>487</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>77</v>
+        <v>488</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>77</v>
+        <v>479</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>77</v>
@@ -11927,45 +11944,43 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>356</v>
+        <v>490</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>134</v>
+        <v>491</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>357</v>
+        <v>492</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>212</v>
+        <v>494</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -12014,31 +12029,31 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>359</v>
+        <v>489</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>132</v>
+        <v>394</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>77</v>
+        <v>495</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>77</v>
+        <v>479</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>77</v>
@@ -12049,10 +12064,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12063,7 +12078,7 @@
         <v>78</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>77</v>
@@ -12072,19 +12087,21 @@
         <v>77</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>511</v>
+        <v>222</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -12108,13 +12125,13 @@
         <v>77</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>77</v>
+        <v>500</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>77</v>
+        <v>501</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>77</v>
@@ -12132,13 +12149,13 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>77</v>
@@ -12150,38 +12167,38 @@
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>388</v>
+        <v>502</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>225</v>
+        <v>479</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>515</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>77</v>
+        <v>505</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>77</v>
@@ -12193,19 +12210,19 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>215</v>
+        <v>348</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -12230,13 +12247,13 @@
         <v>77</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>521</v>
+        <v>77</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>522</v>
+        <v>77</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>77</v>
@@ -12254,45 +12271,45 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>510</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>526</v>
+        <v>514</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12315,18 +12332,16 @@
         <v>77</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>528</v>
+        <v>160</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>529</v>
+        <v>161</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>530</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>77</v>
       </c>
@@ -12350,13 +12365,13 @@
         <v>77</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>531</v>
+        <v>77</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>532</v>
+        <v>77</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>77</v>
@@ -12374,7 +12389,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>527</v>
+        <v>162</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12386,22 +12401,22 @@
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>533</v>
+        <v>163</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>534</v>
+        <v>77</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>535</v>
+        <v>77</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>536</v>
+        <v>77</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>77</v>
@@ -12409,21 +12424,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>77</v>
@@ -12435,20 +12450,18 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>538</v>
+        <v>296</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>539</v>
+        <v>297</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>77</v>
       </c>
@@ -12472,13 +12485,13 @@
         <v>77</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>539</v>
+        <v>77</v>
       </c>
       <c r="Z86" t="s" s="2">
-        <v>542</v>
+        <v>77</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>77</v>
@@ -12496,49 +12509,49 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>537</v>
+        <v>167</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>543</v>
+        <v>163</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>544</v>
+        <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>535</v>
+        <v>77</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>536</v>
+        <v>77</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>545</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>546</v>
+        <v>517</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>546</v>
+        <v>517</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12551,25 +12564,25 @@
         <v>77</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>547</v>
+        <v>363</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>548</v>
+        <v>364</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>549</v>
+        <v>218</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>550</v>
+        <v>219</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>77</v>
@@ -12594,13 +12607,13 @@
         <v>77</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>551</v>
+        <v>77</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>552</v>
+        <v>77</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>77</v>
@@ -12618,7 +12631,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>546</v>
+        <v>365</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12630,19 +12643,19 @@
         <v>77</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>553</v>
+        <v>132</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>554</v>
+        <v>77</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>535</v>
+        <v>77</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>77</v>
@@ -12653,10 +12666,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12679,20 +12692,16 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>158</v>
+        <v>519</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>556</v>
+        <v>520</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
@@ -12740,7 +12749,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12749,7 +12758,7 @@
         <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>560</v>
+        <v>77</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -12758,27 +12767,27 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>561</v>
+        <v>394</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>562</v>
+        <v>522</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>535</v>
+        <v>232</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>563</v>
+        <v>77</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>77</v>
+        <v>523</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>524</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>564</v>
+        <v>524</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12801,17 +12810,19 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>565</v>
+        <v>525</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>527</v>
+      </c>
       <c r="O89" t="s" s="2">
-        <v>559</v>
+        <v>528</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12836,13 +12847,13 @@
         <v>77</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>77</v>
+        <v>529</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>77</v>
+        <v>530</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>77</v>
@@ -12860,7 +12871,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>564</v>
+        <v>524</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12878,27 +12889,27 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>567</v>
+        <v>531</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>568</v>
+        <v>532</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>535</v>
+        <v>232</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>77</v>
+        <v>533</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>77</v>
+        <v>534</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>569</v>
+        <v>535</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>569</v>
+        <v>535</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12918,22 +12929,20 @@
         <v>77</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>570</v>
+        <v>222</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>571</v>
+        <v>536</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>574</v>
+        <v>538</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -12958,13 +12967,13 @@
         <v>77</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>77</v>
+        <v>539</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>77</v>
+        <v>540</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>77</v>
@@ -12982,7 +12991,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>569</v>
+        <v>535</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12991,7 +13000,7 @@
         <v>89</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>560</v>
+        <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>101</v>
@@ -13000,16 +13009,16 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>575</v>
+        <v>541</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>576</v>
+        <v>542</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>77</v>
+        <v>544</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>77</v>
@@ -13017,10 +13026,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13031,7 +13040,7 @@
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>77</v>
@@ -13043,17 +13052,19 @@
         <v>77</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>342</v>
+        <v>222</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>578</v>
+        <v>546</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="O91" t="s" s="2">
-        <v>580</v>
+        <v>549</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -13078,13 +13089,13 @@
         <v>77</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>77</v>
+        <v>547</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>77</v>
+        <v>550</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>77</v>
@@ -13102,13 +13113,13 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>77</v>
@@ -13120,27 +13131,27 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>582</v>
+        <v>552</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>77</v>
+        <v>544</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>77</v>
+        <v>553</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>583</v>
+        <v>554</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>583</v>
+        <v>554</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13151,7 +13162,7 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>77</v>
@@ -13163,16 +13174,20 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>158</v>
+        <v>222</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>159</v>
+        <v>555</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
       </c>
@@ -13196,13 +13211,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>77</v>
+        <v>559</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>77</v>
+        <v>560</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -13220,31 +13235,31 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>161</v>
+        <v>554</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>162</v>
+        <v>561</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>77</v>
+        <v>562</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>77</v>
+        <v>543</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>77</v>
@@ -13255,21 +13270,21 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>77</v>
@@ -13278,21 +13293,23 @@
         <v>77</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>290</v>
+        <v>564</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>291</v>
+        <v>565</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
       </c>
@@ -13340,34 +13357,34 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>167</v>
+        <v>563</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>77</v>
+        <v>568</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>162</v>
+        <v>569</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>77</v>
+        <v>570</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>77</v>
+        <v>543</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>77</v>
+        <v>571</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>77</v>
@@ -13375,45 +13392,43 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>357</v>
+        <v>573</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>211</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>212</v>
+        <v>567</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -13462,31 +13477,31 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>359</v>
+        <v>572</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>132</v>
+        <v>575</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>77</v>
+        <v>576</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>77</v>
+        <v>543</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>77</v>
@@ -13497,10 +13512,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13508,7 +13523,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>89</v>
@@ -13520,19 +13535,23 @@
         <v>77</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>158</v>
+        <v>578</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+        <v>580</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
       </c>
@@ -13580,16 +13599,16 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>77</v>
+        <v>568</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>101</v>
@@ -13598,13 +13617,13 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>494</v>
+        <v>583</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>77</v>
@@ -13615,10 +13634,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13626,10 +13645,10 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>77</v>
@@ -13641,19 +13660,17 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>591</v>
+        <v>348</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>587</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
@@ -13702,13 +13719,13 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>77</v>
@@ -13720,23 +13737,623 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AM96" t="s" s="2">
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AM100" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="AN96" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP96" t="s" s="2">
+      <c r="AN100" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP96">
+  <autoFilter ref="A1:AP101">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13746,7 +14363,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI95">
+  <conditionalFormatting sqref="A2:AI100">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/currentbuild/StructureDefinition-no-basis-auditevent.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-auditevent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-17T09:59:20+00:00</t>
+    <t>2024-04-06T16:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Norway (https://github.com/HL7Norway)</t>
   </si>
   <si>
     <t>Description</t>

--- a/currentbuild/StructureDefinition-no-basis-auditevent.xlsx
+++ b/currentbuild/StructureDefinition-no-basis-auditevent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-06T16:49:55+00:00</t>
+    <t>2024-04-28T16:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This is the main profile that describes the mapping [Norwegian Trust Framework attributes ("Tillitsrammeverk")](https://github.com/NorskHelsenett/Tillitsrammeverk/blob/main/specs/informasjons_og_datamodell.md#424-oppsummering-av-informasjonselementer) to AuditEvent Resource.</t>
+    <t>This is the main profile that describes the mapping of [Norwegian Trust Framework attributes ("Tillitsrammeverk")](https://github.com/NorskHelsenett/Tillitsrammeverk/blob/main/specs/informasjons_og_datamodell.md#424-oppsummering-av-informasjonselementer) to AuditEvent Resource.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1217,7 +1217,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/AuditEventNorwayPractitionerRole)
+    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/auditevent-practitionerrole)
 </t>
   </si>
   <si>
